--- a/examples/Donepezil/CEREBRO_X_Completed_Data_Donepezil.xlsx
+++ b/examples/Donepezil/CEREBRO_X_Completed_Data_Donepezil.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-05T07:58:26Z  | Pipeline: v20  | Source: CEREBRO_Input_Donepezil.xlsx</t>
+          <t>Generated: 2026-09-05T19:24:12Z  | Pipeline: v20  | Source: CEREBRO_Input_Donepezil.xlsx</t>
         </is>
       </c>
     </row>
@@ -11611,21 +11611,21 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>54.28</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
         <is>
-          <t>Resolved clinical half-life (bundle tier 1); Mahmood 2007 exponents shown for re</t>
+          <t>Resolved clinical half-life (bundle tier 6); Mahmood 2007 exponents shown for re</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -37436,20 +37436,20 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>54.28</v>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Resolved clinical half-life (bundle tier 1); Mahmood 2007 exponents shown for reference only (half-life ~ BW^0.25, clearance ~ BW^0.75, volume ~ BW^1.0) -- not applied, since no animal PK value exists</t>
+          <t>Resolved clinical half-life (bundle tier 6); Mahmood 2007 exponents shown for reference only (half-life ~ BW^0.25, clearance ~ BW^0.75, volume ~ BW^1.0) -- not applied, since no animal PK value exists</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -37459,7 +37459,7 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical t½ = 70.0h (human clinical source, bundle tier 1). Reference allometric exponents (Mahmood 2007) for a genuine animal-to-human extrapolation, if one were available: clearance ~384.9×, volume </t>
+          <t>Clinical t½ = 54.3h (population regression / class estimate, bundle tier 6). Reference allometric exponents (Mahmood 2007) for a genuine animal-to-human extrapolation, if one were available: clearance</t>
         </is>
       </c>
     </row>
